--- a/data/cities/us/ca/berkeley/source/Berkeley_Budget_FY25-FY28.xlsx
+++ b/data/cities/us/ca/berkeley/source/Berkeley_Budget_FY25-FY28.xlsx
@@ -1087,7 +1087,7 @@
     <t xml:space="preserve">Enterprise Fund</t>
   </si>
   <si>
-    <t xml:space="preserve">A fund for a service expected to pay for itself through its own fees/charges (e.g., Marina berths, parking). When it can't, it leans on the General Fund.</t>
+    <t xml:space="preserve">A fund for a service expected to pay for itself through its own fees/charges (e.g., Marina berths, parking). When it can't, the General Fund covers the difference.</t>
   </si>
   <si>
     <t xml:space="preserve">Special Fund / Special Revenue Fund</t>
